--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487944_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487944_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.1416</v>
+        <v>8.6739</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7509</v>
+        <v>6.2832</v>
       </c>
       <c r="F2" t="n">
         <v>2.3907</v>
@@ -610,10 +610,10 @@
         <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1541</v>
+        <v>0.6864</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3378</v>
+        <v>0.8701</v>
       </c>
       <c r="U2" t="n">
         <v>-0.1837</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5625</v>
+        <v>4.9335</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8141</v>
+        <v>2.5502</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7484</v>
+        <v>2.3834</v>
       </c>
       <c r="G3" t="n">
         <v>1.9744</v>
@@ -688,13 +688,13 @@
         <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7843</v>
+        <v>1.1553</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2754</v>
+        <v>1.0115</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5089</v>
+        <v>0.1438</v>
       </c>
       <c r="V3" t="n">
         <v>1.0109</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5459</v>
+        <v>3.4617</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7885</v>
+        <v>2.957</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7574</v>
+        <v>0.5047</v>
       </c>
       <c r="G4" t="n">
         <v>3.8395</v>
@@ -766,13 +766,13 @@
         <v>0.7929</v>
       </c>
       <c r="S4" t="n">
-        <v>2.647</v>
+        <v>1.5628</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5442</v>
+        <v>1.7126</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1028</v>
+        <v>-0.1499</v>
       </c>
       <c r="V4" t="n">
         <v>-1.5441</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>P. TRUÑO SOMS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8734</v>
+        <v>1.208</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5913</v>
+        <v>1.208</v>
       </c>
       <c r="F5" t="n">
-        <v>0.282</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9665</v>
+        <v>1.208</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4765</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.4431</v>
+        <v>0.6027</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6578000000000001</v>
+        <v>1.208</v>
       </c>
       <c r="K5" t="n">
-        <v>1.259</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.9169</v>
+        <v>0.6027</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3087</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5262</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4524</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1036</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3488</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1367</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. TRUÑO SOMS</t>
+          <t>P. ÁVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,28 +877,28 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.208</v>
+        <v>0.9053</v>
       </c>
       <c r="E6" t="n">
-        <v>1.208</v>
+        <v>0.9053</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.208</v>
+        <v>0.9053</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.3027</v>
       </c>
       <c r="I6" t="n">
         <v>0.6027</v>
       </c>
       <c r="J6" t="n">
-        <v>1.208</v>
+        <v>0.9053</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.3027</v>
       </c>
       <c r="L6" t="n">
         <v>0.6027</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ÁVALOS ORTIZ</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9053</v>
+        <v>0.8541</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9053</v>
+        <v>0.862</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9053</v>
+        <v>1.435</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3027</v>
+        <v>1.7717</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6027</v>
+        <v>-0.3367</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9053</v>
+        <v>2.5569</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3027</v>
+        <v>1.8298</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6027</v>
+        <v>0.7271</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-1.1219</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.0581</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1.0638</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.6085</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.4856</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.1229</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5991</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0286</v>
+        <v>-1.0029</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6277</v>
+        <v>1.7725</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0066</v>
+        <v>1.7021</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9085</v>
+        <v>0.7397</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.915</v>
+        <v>0.9625</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5788</v>
+        <v>-0.1003</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2176</v>
+        <v>0.0409</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.7963</v>
+        <v>-0.1413</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5722</v>
+        <v>1.8025</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6909</v>
+        <v>0.6988</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1187</v>
+        <v>1.1037</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.784</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1982</v>
+        <v>-2.9733</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1982</v>
+        <v>1.1893</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2796</v>
+        <v>0.8516</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4223</v>
+        <v>0.8637</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8573</v>
+        <v>-0.0122</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.674</v>
+        <v>1.2071</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2053</v>
+        <v>0.2495</v>
       </c>
       <c r="E9" t="n">
-        <v>0.494</v>
+        <v>0.1302</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2887</v>
+        <v>0.1193</v>
       </c>
       <c r="G9" t="n">
-        <v>1.435</v>
+        <v>-0.35</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7717</v>
+        <v>-0.97</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3367</v>
+        <v>0.62</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5569</v>
+        <v>-0.1168</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8298</v>
+        <v>-1.2574</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7271</v>
+        <v>1.1405</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1219</v>
+        <v>-0.2331</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0581</v>
+        <v>0.2874</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0638</v>
+        <v>-0.5205</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1893</v>
+        <v>0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1805</v>
+        <v>-0.1982</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9911</v>
+        <v>0.3964</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0403</v>
+        <v>0.5974</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1176</v>
+        <v>0.4452</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1579</v>
+        <v>0.1522</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.1962</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0581</v>
+        <v>0.0251</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1072</v>
+        <v>-1.2094</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0491</v>
+        <v>1.2346</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.35</v>
+        <v>-0.0066</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.97</v>
+        <v>1.9085</v>
       </c>
       <c r="I10" t="n">
-        <v>0.62</v>
+        <v>-1.915</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1168</v>
+        <v>-0.5788</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2574</v>
+        <v>1.2176</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1405</v>
+        <v>-1.7963</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2331</v>
+        <v>0.5722</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2874</v>
+        <v>0.6909</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5205</v>
+        <v>-0.1187</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.1982</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="S10" t="n">
-        <v>0.406</v>
+        <v>0.7057</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4223</v>
+        <v>0.2415</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0163</v>
+        <v>0.4642</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1962</v>
+        <v>-0.674</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1962</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. JIMENEZ EXPOSITO</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5869</v>
+        <v>-0.0905</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0202</v>
+        <v>0.3294</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6071</v>
+        <v>-0.4199</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7852</v>
+        <v>-0.9665</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3834</v>
+        <v>1.4765</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4018</v>
+        <v>-2.4431</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0202</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0202</v>
+        <v>1.259</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-1.9169</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8053</v>
+        <v>-0.3087</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4036</v>
+        <v>0.2175</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4018</v>
+        <v>-0.5262</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1982</v>
+        <v>0.5947</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1982</v>
+        <v>1.5858</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.4885</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.8417</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.6468</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.3438</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>D. JIMENEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6079</v>
+        <v>-0.3832</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9031</v>
+        <v>0.2239</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2952</v>
+        <v>-0.6071</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7021</v>
+        <v>-0.7852</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7397</v>
+        <v>-0.3834</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9625</v>
+        <v>-0.4018</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1003</v>
+        <v>0.0202</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0409</v>
+        <v>0.0202</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1413</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8025</v>
+        <v>-0.8053</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6988</v>
+        <v>-0.4036</v>
       </c>
       <c r="O12" t="n">
-        <v>1.1037</v>
+        <v>-0.4018</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.784</v>
+        <v>0.1982</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1893</v>
+        <v>0.1982</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.526</v>
+        <v>0.2037</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0365</v>
+        <v>0.2037</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4895</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1117</v>
+        <v>-0.8142</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4566</v>
+        <v>-1.4961</v>
       </c>
       <c r="F13" t="n">
-        <v>0.345</v>
+        <v>0.6819</v>
       </c>
       <c r="G13" t="n">
         <v>-1.3634</v>
@@ -1468,13 +1468,13 @@
         <v>0.9911</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5183</v>
+        <v>0.8158</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0683</v>
+        <v>1.0289</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.55</v>
+        <v>-0.213</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2666</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.3596</v>
+        <v>-1.1119</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.9144</v>
+        <v>-3.116</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5549</v>
+        <v>2.0041</v>
       </c>
       <c r="G14" t="n">
         <v>2.4616</v>
@@ -1546,13 +1546,13 @@
         <v>1.1893</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8567</v>
+        <v>0.3909</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3706</v>
+        <v>0.4278</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4861</v>
+        <v>-0.0369</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>17.4331</v>
+        <v>18.681</v>
       </c>
       <c r="E15" t="n">
-        <v>7.376799999999999</v>
+        <v>8.6248</v>
       </c>
       <c r="F15" t="n">
-        <v>10.0564</v>
+        <v>10.0563</v>
       </c>
       <c r="G15" t="n">
         <v>16.4559</v>
@@ -1594,25 +1594,25 @@
         <v>11.137</v>
       </c>
       <c r="I15" t="n">
-        <v>5.319100000000001</v>
+        <v>5.319099999999999</v>
       </c>
       <c r="J15" t="n">
         <v>11.3457</v>
       </c>
       <c r="K15" t="n">
-        <v>6.905099999999999</v>
+        <v>6.905100000000001</v>
       </c>
       <c r="L15" t="n">
         <v>4.4403</v>
       </c>
       <c r="M15" t="n">
-        <v>5.1105</v>
+        <v>5.110500000000001</v>
       </c>
       <c r="N15" t="n">
         <v>4.2319</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8786</v>
+        <v>0.8785999999999998</v>
       </c>
       <c r="P15" t="n">
         <v>-3.9644</v>
@@ -1624,13 +1624,13 @@
         <v>10.9021</v>
       </c>
       <c r="S15" t="n">
-        <v>7.8187</v>
+        <v>9.066599999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>6.8844</v>
+        <v>8.132300000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9342999999999997</v>
+        <v>0.9341999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-2.8771</v>
@@ -1639,7 +1639,7 @@
         <v>4.0137</v>
       </c>
       <c r="X15" t="n">
-        <v>-6.890700000000001</v>
+        <v>-6.8907</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6552</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="E16" t="n">
         <v>-0.6856</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3408</v>
+        <v>1.4159</v>
       </c>
       <c r="G16" t="n">
         <v>1.3011</v>
@@ -1702,13 +1702,13 @@
         <v>2.3787</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5003</v>
+        <v>-1.4252</v>
       </c>
       <c r="T16" t="n">
         <v>-0.9432</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5571</v>
+        <v>-0.482</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5331</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GARCIA GUERRERO</t>
+          <t>H. FERNANDEZ CAMPOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0046</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4114</v>
+        <v>0.5614</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.416</v>
+        <v>-0.6251</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4121</v>
+        <v>-1.5178</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5177</v>
+        <v>-0.7504999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9298</v>
+        <v>-0.7673</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0442</v>
+        <v>-0.2811</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0404</v>
+        <v>-0.968</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0039</v>
+        <v>0.6869</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4563</v>
+        <v>-1.2367</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4774</v>
+        <v>0.2175</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9337</v>
+        <v>-1.4542</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4075</v>
+        <v>-0.1495</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3671</v>
+        <v>0.3599</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0403</v>
+        <v>-0.5094</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. FERNANDEZ CAMPOS</t>
+          <t>M. PEREZ SARRABLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5084</v>
+        <v>-0.2297</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5614</v>
+        <v>0.9484</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0698</v>
+        <v>-1.1781</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5178</v>
+        <v>-0.1215</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7504999999999999</v>
+        <v>0.9345</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7673</v>
+        <v>-1.056</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2811</v>
+        <v>1.5227</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.968</v>
+        <v>0.9887</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6869</v>
+        <v>0.534</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2367</v>
+        <v>-1.6442</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2175</v>
+        <v>-0.0542</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4542</v>
+        <v>-1.59</v>
       </c>
       <c r="P19" t="n">
         <v>0.3964</v>
@@ -1936,28 +1936,28 @@
         <v>1.3876</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5942</v>
+        <v>-0.5047</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3599</v>
+        <v>0.4168</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.9215</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. PEREZ SARRABLO</t>
+          <t>A. GARCIA GUERRERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9768</v>
+        <v>-0.3102</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3371</v>
+        <v>0.1058</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3139</v>
+        <v>-0.416</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1215</v>
+        <v>-0.4121</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9345</v>
+        <v>0.5177</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.056</v>
+        <v>-0.9298</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5227</v>
+        <v>0.0442</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9887</v>
+        <v>0.0404</v>
       </c>
       <c r="L20" t="n">
-        <v>0.534</v>
+        <v>0.0039</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6442</v>
+        <v>-0.4563</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0542</v>
+        <v>0.4774</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.59</v>
+        <v>-0.9337</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2517</v>
+        <v>0.1019</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1944</v>
+        <v>0.0615</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0573</v>
+        <v>0.0403</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. CABARROCAS MARTIN</t>
+          <t>D. GARZON ALVAREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.04</v>
+        <v>-0.8739</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5646</v>
+        <v>0.4883</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6046</v>
+        <v>-1.3623</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0017</v>
+        <v>-3.8145</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0054</v>
+        <v>-2.3795</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0071</v>
+        <v>-1.435</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2894</v>
+        <v>-1.2373</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4099</v>
+        <v>-0.0398</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1205</v>
+        <v>-1.1975</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7123</v>
+        <v>-2.5771</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4153</v>
+        <v>-2.3397</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.1276</v>
+        <v>-0.2374</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7929</v>
+        <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3054</v>
+        <v>-0.3349</v>
       </c>
       <c r="T21" t="n">
-        <v>1.854</v>
+        <v>0.036</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5485</v>
+        <v>-0.3709</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1367</v>
+        <v>2.6808</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.6808</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. GARZON ALVAREZ</t>
+          <t>J. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0463</v>
+        <v>-0.9979</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3865</v>
+        <v>-0.1248</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4328</v>
+        <v>-0.8731</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.8145</v>
+        <v>-0.7372</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.3795</v>
+        <v>-0.8731</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.435</v>
+        <v>0.1358</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2373</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0398</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1975</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5771</v>
+        <v>-0.7372</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.3397</v>
+        <v>-0.8731</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2374</v>
+        <v>0.1358</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5073</v>
+        <v>-0.2606</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0658</v>
+        <v>-0.1248</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4415</v>
+        <v>-0.1358</v>
       </c>
       <c r="V22" t="n">
-        <v>2.6808</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.6808</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. LOPEZ SANCHEZ</t>
+          <t>E. GEA BECERRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1337</v>
+        <v>-1.7762</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1248</v>
+        <v>-1.7895</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0089</v>
+        <v>0.0134</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7372</v>
+        <v>-0.5769</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8731</v>
+        <v>-0.5596</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1358</v>
+        <v>-0.0174</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.3004</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.8953</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.5949</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7372</v>
+        <v>-0.8773</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8731</v>
+        <v>-1.4548</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1358</v>
+        <v>0.5775</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.7751</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3964</v>
+        <v>-1.1774</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1248</v>
+        <v>-0.1631</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2717</v>
+        <v>-1.0143</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.8148</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.0554</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. GEA BECERRA</t>
+          <t>R. CABARROCAS MARTIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2818</v>
+        <v>-2.0352</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7708</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.511</v>
+        <v>-2.5811</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5769</v>
+        <v>-2.0017</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5596</v>
+        <v>0.0054</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0174</v>
+        <v>-2.0071</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3004</v>
+        <v>-0.2894</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8953</v>
+        <v>-0.4099</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5949</v>
+        <v>0.1205</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8773</v>
+        <v>-1.7123</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4548</v>
+        <v>0.4153</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5775</v>
+        <v>-2.1276</v>
       </c>
       <c r="P24" t="n">
         <v>0.7929</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7751</v>
+        <v>0.7929</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6830000000000001</v>
+        <v>0.3103</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8556</v>
+        <v>0.8353</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5387</v>
+        <v>-0.525</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.8148</v>
+        <v>-1.1367</v>
       </c>
       <c r="W24" t="n">
-        <v>0.0554</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.8701</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.6092</v>
+        <v>-5.0985</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.8395</v>
+        <v>-6.432</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2303</v>
+        <v>1.3335</v>
       </c>
       <c r="G25" t="n">
         <v>-4.1139</v>
@@ -2404,13 +2404,13 @@
         <v>1.9822</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3237</v>
+        <v>-0.8131</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.057</v>
+        <v>-0.6495</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2668</v>
+        <v>-0.1636</v>
       </c>
       <c r="V25" t="n">
         <v>1.8107</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.0929</v>
+        <v>-5.3461</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.502</v>
+        <v>-4.2795</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.5909</v>
+        <v>-1.0665</v>
       </c>
       <c r="G26" t="n">
         <v>-5.0669</v>
@@ -2482,13 +2482,13 @@
         <v>2.5769</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.2748</v>
+        <v>-1.528</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.9857</v>
+        <v>-0.7632</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.2891</v>
+        <v>-0.7647</v>
       </c>
       <c r="V26" t="n">
         <v>-0.337</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-17.4332</v>
+        <v>-15.3958</v>
       </c>
       <c r="E27" t="n">
-        <v>-10.0564</v>
+        <v>-10.0563</v>
       </c>
       <c r="F27" t="n">
-        <v>-7.376800000000001</v>
+        <v>-5.339399999999999</v>
       </c>
       <c r="G27" t="n">
         <v>-16.4561</v>
@@ -2560,13 +2560,13 @@
         <v>14.8668</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.818499999999999</v>
+        <v>-5.7812</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9342999999999999</v>
+        <v>-0.9343</v>
       </c>
       <c r="U27" t="n">
-        <v>-6.884499999999999</v>
+        <v>-4.8469</v>
       </c>
       <c r="V27" t="n">
         <v>2.877</v>
